--- a/chapters/06/core/AIHE-B02/supp/AIHE-EX17/xlsx/AIHE-EX17_workbook.xlsx
+++ b/chapters/06/core/AIHE-B02/supp/AIHE-EX17/xlsx/AIHE-EX17_workbook.xlsx
@@ -85,12 +85,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="centre"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -106,10 +106,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -117,10 +117,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="centre" vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -170,7 +170,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -178,7 +178,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="centre" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
